--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113291537</v>
+        <v>113291517</v>
       </c>
       <c r="B18" t="n">
-        <v>104364</v>
+        <v>94870</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,25 +2654,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446617</v>
+        <v>446675</v>
       </c>
       <c r="R18" t="n">
-        <v>6585536</v>
+        <v>6585643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2749,10 +2749,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113291530</v>
+        <v>113291537</v>
       </c>
       <c r="B19" t="n">
-        <v>5186</v>
+        <v>104380</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2765,32 +2765,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2798,10 +2793,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446657</v>
+        <v>446617</v>
       </c>
       <c r="R19" t="n">
-        <v>6585635</v>
+        <v>6585536</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2864,7 +2859,7 @@
         <v>113291547</v>
       </c>
       <c r="B20" t="n">
-        <v>93938</v>
+        <v>93954</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2979,7 +2974,7 @@
         <v>113291551</v>
       </c>
       <c r="B21" t="n">
-        <v>104364</v>
+        <v>104380</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3083,10 +3078,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113291517</v>
+        <v>113291530</v>
       </c>
       <c r="B22" t="n">
-        <v>94854</v>
+        <v>5186</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3095,31 +3090,36 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446675</v>
+        <v>446657</v>
       </c>
       <c r="R22" t="n">
-        <v>6585643</v>
+        <v>6585635</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113291517</v>
+        <v>113291547</v>
       </c>
       <c r="B18" t="n">
-        <v>94870</v>
+        <v>93954</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,29 +2654,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2686,10 +2694,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446675</v>
+        <v>446595</v>
       </c>
       <c r="R18" t="n">
-        <v>6585643</v>
+        <v>6585605</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2856,10 +2864,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113291547</v>
+        <v>113291551</v>
       </c>
       <c r="B20" t="n">
-        <v>93954</v>
+        <v>104380</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2872,33 +2880,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446595</v>
+        <v>446630</v>
       </c>
       <c r="R20" t="n">
-        <v>6585605</v>
+        <v>6585625</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113291551</v>
+        <v>113291517</v>
       </c>
       <c r="B21" t="n">
-        <v>104380</v>
+        <v>94870</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2983,25 +2983,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446630</v>
+        <v>446675</v>
       </c>
       <c r="R21" t="n">
-        <v>6585625</v>
+        <v>6585643</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113291547</v>
+        <v>113291517</v>
       </c>
       <c r="B18" t="n">
-        <v>93954</v>
+        <v>94882</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,37 +2654,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2694,10 +2686,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446595</v>
+        <v>446675</v>
       </c>
       <c r="R18" t="n">
-        <v>6585605</v>
+        <v>6585643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2757,10 +2749,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113291537</v>
+        <v>113291547</v>
       </c>
       <c r="B19" t="n">
-        <v>104380</v>
+        <v>93966</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2773,25 +2765,33 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446617</v>
+        <v>446595</v>
       </c>
       <c r="R19" t="n">
-        <v>6585536</v>
+        <v>6585605</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2864,10 +2864,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113291551</v>
+        <v>113291537</v>
       </c>
       <c r="B20" t="n">
-        <v>104380</v>
+        <v>104394</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446630</v>
+        <v>446617</v>
       </c>
       <c r="R20" t="n">
-        <v>6585625</v>
+        <v>6585536</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113291517</v>
+        <v>113291551</v>
       </c>
       <c r="B21" t="n">
-        <v>94870</v>
+        <v>104394</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2983,25 +2983,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446675</v>
+        <v>446630</v>
       </c>
       <c r="R21" t="n">
-        <v>6585643</v>
+        <v>6585625</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113291517</v>
+        <v>113291537</v>
       </c>
       <c r="B18" t="n">
-        <v>94882</v>
+        <v>104394</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,25 +2654,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446675</v>
+        <v>446617</v>
       </c>
       <c r="R18" t="n">
-        <v>6585643</v>
+        <v>6585536</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2864,10 +2864,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113291537</v>
+        <v>113291517</v>
       </c>
       <c r="B20" t="n">
-        <v>104394</v>
+        <v>94882</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2876,25 +2876,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446617</v>
+        <v>446675</v>
       </c>
       <c r="R20" t="n">
-        <v>6585536</v>
+        <v>6585643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113291551</v>
+        <v>113291530</v>
       </c>
       <c r="B21" t="n">
-        <v>104394</v>
+        <v>5186</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2987,27 +2987,32 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3015,10 +3020,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446630</v>
+        <v>446657</v>
       </c>
       <c r="R21" t="n">
-        <v>6585625</v>
+        <v>6585635</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3078,10 +3083,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113291530</v>
+        <v>113291551</v>
       </c>
       <c r="B22" t="n">
-        <v>5186</v>
+        <v>104394</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3094,32 +3099,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446657</v>
+        <v>446630</v>
       </c>
       <c r="R22" t="n">
-        <v>6585635</v>
+        <v>6585625</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113291537</v>
+        <v>113291530</v>
       </c>
       <c r="B18" t="n">
-        <v>104394</v>
+        <v>5186</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2658,27 +2658,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2686,10 +2691,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446617</v>
+        <v>446657</v>
       </c>
       <c r="R18" t="n">
-        <v>6585536</v>
+        <v>6585635</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2749,10 +2754,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113291547</v>
+        <v>113291517</v>
       </c>
       <c r="B19" t="n">
-        <v>93966</v>
+        <v>94904</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2761,37 +2766,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2801,10 +2798,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446595</v>
+        <v>446675</v>
       </c>
       <c r="R19" t="n">
-        <v>6585605</v>
+        <v>6585643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2864,10 +2861,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113291517</v>
+        <v>113291537</v>
       </c>
       <c r="B20" t="n">
-        <v>94882</v>
+        <v>104416</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2876,25 +2873,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2908,10 +2905,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446675</v>
+        <v>446617</v>
       </c>
       <c r="R20" t="n">
-        <v>6585643</v>
+        <v>6585536</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,10 +2968,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113291530</v>
+        <v>113291547</v>
       </c>
       <c r="B21" t="n">
-        <v>5186</v>
+        <v>93988</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2987,32 +2984,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446657</v>
+        <v>446595</v>
       </c>
       <c r="R21" t="n">
-        <v>6585635</v>
+        <v>6585605</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3086,7 +3086,7 @@
         <v>113291551</v>
       </c>
       <c r="B22" t="n">
-        <v>104394</v>
+        <v>104416</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -2754,10 +2754,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113291517</v>
+        <v>113291551</v>
       </c>
       <c r="B19" t="n">
-        <v>94904</v>
+        <v>104420</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2766,25 +2766,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446675</v>
+        <v>446630</v>
       </c>
       <c r="R19" t="n">
-        <v>6585643</v>
+        <v>6585625</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113291537</v>
+        <v>113291547</v>
       </c>
       <c r="B20" t="n">
-        <v>104416</v>
+        <v>93992</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2877,25 +2877,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2905,10 +2913,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446617</v>
+        <v>446595</v>
       </c>
       <c r="R20" t="n">
-        <v>6585536</v>
+        <v>6585605</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2968,10 +2976,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113291547</v>
+        <v>113291517</v>
       </c>
       <c r="B21" t="n">
-        <v>93988</v>
+        <v>94908</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2980,37 +2988,29 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446595</v>
+        <v>446675</v>
       </c>
       <c r="R21" t="n">
-        <v>6585605</v>
+        <v>6585643</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113291551</v>
+        <v>113291537</v>
       </c>
       <c r="B22" t="n">
-        <v>104416</v>
+        <v>104420</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446630</v>
+        <v>446617</v>
       </c>
       <c r="R22" t="n">
-        <v>6585625</v>
+        <v>6585536</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -2976,10 +2976,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113291517</v>
+        <v>113291537</v>
       </c>
       <c r="B21" t="n">
-        <v>94908</v>
+        <v>104420</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2988,25 +2988,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446675</v>
+        <v>446617</v>
       </c>
       <c r="R21" t="n">
-        <v>6585643</v>
+        <v>6585536</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113291537</v>
+        <v>113291517</v>
       </c>
       <c r="B22" t="n">
-        <v>104420</v>
+        <v>94908</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3095,25 +3095,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446617</v>
+        <v>446675</v>
       </c>
       <c r="R22" t="n">
-        <v>6585536</v>
+        <v>6585643</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113291530</v>
+        <v>113291517</v>
       </c>
       <c r="B18" t="n">
-        <v>5186</v>
+        <v>94914</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,36 +2654,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2691,10 +2686,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446657</v>
+        <v>446675</v>
       </c>
       <c r="R18" t="n">
-        <v>6585635</v>
+        <v>6585643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2754,10 +2749,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113291551</v>
+        <v>113291530</v>
       </c>
       <c r="B19" t="n">
-        <v>104420</v>
+        <v>5186</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2770,27 +2765,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446630</v>
+        <v>446657</v>
       </c>
       <c r="R19" t="n">
-        <v>6585625</v>
+        <v>6585635</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>113291547</v>
       </c>
       <c r="B20" t="n">
-        <v>93992</v>
+        <v>93998</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>113291537</v>
       </c>
       <c r="B21" t="n">
-        <v>104420</v>
+        <v>104426</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113291517</v>
+        <v>113291551</v>
       </c>
       <c r="B22" t="n">
-        <v>94908</v>
+        <v>104426</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3095,25 +3095,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446675</v>
+        <v>446630</v>
       </c>
       <c r="R22" t="n">
-        <v>6585643</v>
+        <v>6585625</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113291517</v>
+        <v>113291530</v>
       </c>
       <c r="B18" t="n">
-        <v>94914</v>
+        <v>5186</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,31 +2654,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2686,10 +2691,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446675</v>
+        <v>446657</v>
       </c>
       <c r="R18" t="n">
-        <v>6585643</v>
+        <v>6585635</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2749,10 +2754,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113291530</v>
+        <v>113291517</v>
       </c>
       <c r="B19" t="n">
-        <v>5186</v>
+        <v>94914</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2761,36 +2766,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446657</v>
+        <v>446675</v>
       </c>
       <c r="R19" t="n">
-        <v>6585635</v>
+        <v>6585643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113291547</v>
+        <v>113291537</v>
       </c>
       <c r="B20" t="n">
-        <v>93998</v>
+        <v>104426</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2877,33 +2877,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2913,10 +2905,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446595</v>
+        <v>446617</v>
       </c>
       <c r="R20" t="n">
-        <v>6585605</v>
+        <v>6585536</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2976,7 +2968,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113291537</v>
+        <v>113291551</v>
       </c>
       <c r="B21" t="n">
         <v>104426</v>
@@ -3020,10 +3012,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446617</v>
+        <v>446630</v>
       </c>
       <c r="R21" t="n">
-        <v>6585536</v>
+        <v>6585625</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3083,10 +3075,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113291551</v>
+        <v>113291547</v>
       </c>
       <c r="B22" t="n">
-        <v>104426</v>
+        <v>93998</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3099,25 +3091,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446630</v>
+        <v>446595</v>
       </c>
       <c r="R22" t="n">
-        <v>6585625</v>
+        <v>6585605</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113291530</v>
+        <v>113291551</v>
       </c>
       <c r="B18" t="n">
-        <v>5186</v>
+        <v>104433</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2658,32 +2658,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2691,10 +2686,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446657</v>
+        <v>446630</v>
       </c>
       <c r="R18" t="n">
-        <v>6585635</v>
+        <v>6585625</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2754,10 +2749,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113291517</v>
+        <v>113291530</v>
       </c>
       <c r="B19" t="n">
-        <v>94914</v>
+        <v>5186</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2766,31 +2761,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446675</v>
+        <v>446657</v>
       </c>
       <c r="R19" t="n">
-        <v>6585643</v>
+        <v>6585635</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113291537</v>
+        <v>113291517</v>
       </c>
       <c r="B20" t="n">
-        <v>104426</v>
+        <v>94921</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2873,25 +2873,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446617</v>
+        <v>446675</v>
       </c>
       <c r="R20" t="n">
-        <v>6585536</v>
+        <v>6585643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113291551</v>
+        <v>113291537</v>
       </c>
       <c r="B21" t="n">
-        <v>104426</v>
+        <v>104433</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446630</v>
+        <v>446617</v>
       </c>
       <c r="R21" t="n">
-        <v>6585625</v>
+        <v>6585536</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3078,7 +3078,7 @@
         <v>113291547</v>
       </c>
       <c r="B22" t="n">
-        <v>93998</v>
+        <v>94005</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3854,6 +3854,1446 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123515262</v>
+      </c>
+      <c r="B29" t="n">
+        <v>83383</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>446659</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6585649</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123516577</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57634</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>446649</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6585666</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123519051</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83386</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>N om Skinnerud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>446580</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6585527</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123516543</v>
+      </c>
+      <c r="B32" t="n">
+        <v>83383</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>446597</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6585597</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123515258</v>
+      </c>
+      <c r="B33" t="n">
+        <v>105482</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>446629</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6585726</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123519055</v>
+      </c>
+      <c r="B34" t="n">
+        <v>83386</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>N om Skinnerud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>446600</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6585508</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123516522</v>
+      </c>
+      <c r="B35" t="n">
+        <v>83383</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>446600</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6585730</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Barkborredödade granar intill och kantzon från hygge.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123519050</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91586</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>N om Skinnerud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>446696</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6585518</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123515263</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>446669</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6585514</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123516564</v>
+      </c>
+      <c r="B38" t="n">
+        <v>105482</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>446625</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6585724</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123516643</v>
+      </c>
+      <c r="B39" t="n">
+        <v>105482</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>446604</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6585606</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123516584</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90963</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>446651</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6585639</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123516626</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90396</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>446625</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6585622</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -3856,10 +3856,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123515262</v>
+        <v>123516553</v>
       </c>
       <c r="B29" t="n">
-        <v>83383</v>
+        <v>83386</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,17 +3889,24 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446659</v>
+        <v>446597</v>
       </c>
       <c r="R29" t="n">
-        <v>6585649</v>
+        <v>6585597</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3940,28 +3947,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123516577</v>
+        <v>123515258</v>
       </c>
       <c r="B30" t="n">
-        <v>57634</v>
+        <v>105485</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3970,50 +3982,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446649</v>
+        <v>446629</v>
       </c>
       <c r="R30" t="n">
-        <v>6585666</v>
+        <v>6585726</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,22 +4060,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123519051</v>
+        <v>123515263</v>
       </c>
       <c r="B31" t="n">
-        <v>83386</v>
+        <v>5173</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4084,47 +4084,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1445</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446580</v>
+        <v>446669</v>
       </c>
       <c r="R31" t="n">
-        <v>6585527</v>
+        <v>6585514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4171,22 +4162,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123516543</v>
+        <v>123516626</v>
       </c>
       <c r="B32" t="n">
-        <v>83383</v>
+        <v>90399</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4195,30 +4186,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1445</v>
+        <v>4189</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4234,10 +4225,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446597</v>
+        <v>446625</v>
       </c>
       <c r="R32" t="n">
-        <v>6585597</v>
+        <v>6585622</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4293,18 +4284,14 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123515258</v>
+        <v>123516584</v>
       </c>
       <c r="B33" t="n">
-        <v>105482</v>
+        <v>90966</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4313,38 +4300,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446629</v>
+        <v>446651</v>
       </c>
       <c r="R33" t="n">
-        <v>6585726</v>
+        <v>6585639</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4385,25 +4375,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123519055</v>
+        <v>123516522</v>
       </c>
       <c r="B34" t="n">
         <v>83386</v>
@@ -4438,7 +4429,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4446,16 +4437,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>446600</v>
       </c>
       <c r="R34" t="n">
-        <v>6585508</v>
+        <v>6585730</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4490,34 +4483,44 @@
           <t>2025-03-26</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Barkborredödade granar intill och kantzon från hygge.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123516522</v>
+        <v>123519050</v>
       </c>
       <c r="B35" t="n">
-        <v>83383</v>
+        <v>91586</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4526,49 +4529,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446600</v>
+        <v>446696</v>
       </c>
       <c r="R35" t="n">
-        <v>6585730</v>
+        <v>6585518</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4603,44 +4600,34 @@
           <t>2025-03-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Barkborredödade granar intill och kantzon från hygge.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123519050</v>
+        <v>123515262</v>
       </c>
       <c r="B36" t="n">
-        <v>91586</v>
+        <v>83386</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4649,43 +4636,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446696</v>
+        <v>446659</v>
       </c>
       <c r="R36" t="n">
-        <v>6585518</v>
+        <v>6585649</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4732,22 +4714,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123515263</v>
+        <v>123516564</v>
       </c>
       <c r="B37" t="n">
-        <v>5173</v>
+        <v>105485</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4760,34 +4742,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446669</v>
+        <v>446625</v>
       </c>
       <c r="R37" t="n">
-        <v>6585514</v>
+        <v>6585724</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4828,28 +4822,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123516564</v>
+        <v>123516577</v>
       </c>
       <c r="B38" t="n">
-        <v>105482</v>
+        <v>57634</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4858,39 +4853,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4898,10 +4893,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446625</v>
+        <v>446649</v>
       </c>
       <c r="R38" t="n">
-        <v>6585724</v>
+        <v>6585666</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4942,7 +4937,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4961,10 +4955,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123516643</v>
+        <v>123519055</v>
       </c>
       <c r="B39" t="n">
-        <v>105482</v>
+        <v>83386</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4973,50 +4967,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446604</v>
+        <v>446600</v>
       </c>
       <c r="R39" t="n">
-        <v>6585606</v>
+        <v>6585508</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5057,29 +5048,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123516584</v>
+        <v>123516643</v>
       </c>
       <c r="B40" t="n">
-        <v>90963</v>
+        <v>105485</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5088,30 +5078,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5119,10 +5118,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446651</v>
+        <v>446604</v>
       </c>
       <c r="R40" t="n">
-        <v>6585639</v>
+        <v>6585606</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5182,10 +5181,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123516626</v>
+        <v>123519051</v>
       </c>
       <c r="B41" t="n">
-        <v>90396</v>
+        <v>83386</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5194,30 +5193,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4189</v>
+        <v>1445</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5225,18 +5224,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446625</v>
+        <v>446580</v>
       </c>
       <c r="R41" t="n">
-        <v>6585622</v>
+        <v>6585527</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5277,19 +5274,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -3856,10 +3856,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123516553</v>
+        <v>123516584</v>
       </c>
       <c r="B29" t="n">
-        <v>83386</v>
+        <v>90983</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3868,32 +3868,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1445</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3903,10 +3899,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446597</v>
+        <v>446651</v>
       </c>
       <c r="R29" t="n">
-        <v>6585597</v>
+        <v>6585639</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3962,18 +3958,14 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123515258</v>
+        <v>123516577</v>
       </c>
       <c r="B30" t="n">
-        <v>105485</v>
+        <v>57640</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3982,38 +3974,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446629</v>
+        <v>446649</v>
       </c>
       <c r="R30" t="n">
-        <v>6585726</v>
+        <v>6585666</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,22 +4064,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123515263</v>
+        <v>123516626</v>
       </c>
       <c r="B31" t="n">
-        <v>5173</v>
+        <v>90416</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4088,34 +4092,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>4189</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446669</v>
+        <v>446625</v>
       </c>
       <c r="R31" t="n">
-        <v>6585514</v>
+        <v>6585622</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4156,28 +4171,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123516626</v>
+        <v>123519055</v>
       </c>
       <c r="B32" t="n">
-        <v>90399</v>
+        <v>83395</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4186,30 +4202,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4189</v>
+        <v>1445</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4217,18 +4233,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446625</v>
+        <v>446600</v>
       </c>
       <c r="R32" t="n">
-        <v>6585622</v>
+        <v>6585508</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4269,29 +4283,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123516584</v>
+        <v>123515262</v>
       </c>
       <c r="B33" t="n">
-        <v>90966</v>
+        <v>83395</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4300,41 +4313,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1445</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446651</v>
+        <v>446659</v>
       </c>
       <c r="R33" t="n">
-        <v>6585639</v>
+        <v>6585649</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4375,29 +4385,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123516522</v>
+        <v>123516643</v>
       </c>
       <c r="B34" t="n">
-        <v>83386</v>
+        <v>105502</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4406,38 +4415,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4445,10 +4455,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446600</v>
+        <v>446604</v>
       </c>
       <c r="R34" t="n">
-        <v>6585730</v>
+        <v>6585606</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4483,11 +4493,6 @@
           <t>2025-03-26</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Barkborredödade granar intill och kantzon från hygge.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4509,18 +4514,14 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123519050</v>
+        <v>123516553</v>
       </c>
       <c r="B35" t="n">
-        <v>91586</v>
+        <v>83395</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4529,43 +4530,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446696</v>
+        <v>446597</v>
       </c>
       <c r="R35" t="n">
-        <v>6585518</v>
+        <v>6585597</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4606,28 +4609,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123515262</v>
+        <v>123515263</v>
       </c>
       <c r="B36" t="n">
-        <v>83386</v>
+        <v>5174</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4636,25 +4644,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1445</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4664,10 +4672,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446659</v>
+        <v>446669</v>
       </c>
       <c r="R36" t="n">
-        <v>6585649</v>
+        <v>6585514</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4726,10 +4734,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123516564</v>
+        <v>123515258</v>
       </c>
       <c r="B37" t="n">
-        <v>105485</v>
+        <v>105502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4759,29 +4767,17 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446625</v>
+        <v>446629</v>
       </c>
       <c r="R37" t="n">
-        <v>6585724</v>
+        <v>6585726</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4822,29 +4818,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123516577</v>
+        <v>123516522</v>
       </c>
       <c r="B38" t="n">
-        <v>57634</v>
+        <v>83395</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4853,39 +4848,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>1445</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4893,10 +4887,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446649</v>
+        <v>446600</v>
       </c>
       <c r="R38" t="n">
-        <v>6585666</v>
+        <v>6585730</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4931,12 +4925,18 @@
           <t>2025-03-26</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Barkborredödade granar intill och kantzon från hygge.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4951,14 +4951,18 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123519055</v>
+        <v>123519051</v>
       </c>
       <c r="B39" t="n">
-        <v>83386</v>
+        <v>83395</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4990,7 +4994,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5004,10 +5008,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446600</v>
+        <v>446580</v>
       </c>
       <c r="R39" t="n">
-        <v>6585508</v>
+        <v>6585527</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5066,10 +5070,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123516643</v>
+        <v>123516564</v>
       </c>
       <c r="B40" t="n">
-        <v>105485</v>
+        <v>105502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5101,7 +5105,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5118,10 +5122,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446604</v>
+        <v>446625</v>
       </c>
       <c r="R40" t="n">
-        <v>6585606</v>
+        <v>6585724</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5181,10 +5185,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123519051</v>
+        <v>123519050</v>
       </c>
       <c r="B41" t="n">
-        <v>83386</v>
+        <v>91603</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5193,32 +5197,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446580</v>
+        <v>446696</v>
       </c>
       <c r="R41" t="n">
-        <v>6585527</v>
+        <v>6585518</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -4959,10 +4959,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123519051</v>
+        <v>123516564</v>
       </c>
       <c r="B39" t="n">
-        <v>83395</v>
+        <v>105502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4971,47 +4971,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446580</v>
+        <v>446625</v>
       </c>
       <c r="R39" t="n">
-        <v>6585527</v>
+        <v>6585724</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5052,28 +5055,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123516564</v>
+        <v>123519051</v>
       </c>
       <c r="B40" t="n">
-        <v>105502</v>
+        <v>83395</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5082,50 +5086,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446625</v>
+        <v>446580</v>
       </c>
       <c r="R40" t="n">
-        <v>6585724</v>
+        <v>6585527</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5166,19 +5167,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -4959,10 +4959,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123516564</v>
+        <v>123519051</v>
       </c>
       <c r="B39" t="n">
-        <v>105502</v>
+        <v>83395</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4971,50 +4971,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446625</v>
+        <v>446580</v>
       </c>
       <c r="R39" t="n">
-        <v>6585724</v>
+        <v>6585527</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5055,29 +5052,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123519051</v>
+        <v>123516564</v>
       </c>
       <c r="B40" t="n">
-        <v>83395</v>
+        <v>105502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5086,47 +5082,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446580</v>
+        <v>446625</v>
       </c>
       <c r="R40" t="n">
-        <v>6585527</v>
+        <v>6585724</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5167,18 +5166,19 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -3856,10 +3856,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123516584</v>
+        <v>123516553</v>
       </c>
       <c r="B29" t="n">
-        <v>90983</v>
+        <v>83400</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3868,28 +3868,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1445</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3899,10 +3903,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446651</v>
+        <v>446597</v>
       </c>
       <c r="R29" t="n">
-        <v>6585639</v>
+        <v>6585597</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3958,14 +3962,18 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123516577</v>
+        <v>123515258</v>
       </c>
       <c r="B30" t="n">
-        <v>57640</v>
+        <v>105518</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3974,50 +3982,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446649</v>
+        <v>446629</v>
       </c>
       <c r="R30" t="n">
-        <v>6585666</v>
+        <v>6585726</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4064,22 +4060,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123516626</v>
+        <v>123515262</v>
       </c>
       <c r="B31" t="n">
-        <v>90416</v>
+        <v>83400</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4088,49 +4084,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4189</v>
+        <v>1445</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446625</v>
+        <v>446659</v>
       </c>
       <c r="R31" t="n">
-        <v>6585622</v>
+        <v>6585649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4171,29 +4156,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123519055</v>
+        <v>123516584</v>
       </c>
       <c r="B32" t="n">
-        <v>83395</v>
+        <v>90988</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4202,47 +4186,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1445</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446600</v>
+        <v>446651</v>
       </c>
       <c r="R32" t="n">
-        <v>6585508</v>
+        <v>6585639</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4283,28 +4261,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123515262</v>
+        <v>123519055</v>
       </c>
       <c r="B33" t="n">
-        <v>83395</v>
+        <v>83400</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4334,17 +4313,26 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446659</v>
+        <v>446600</v>
       </c>
       <c r="R33" t="n">
-        <v>6585649</v>
+        <v>6585508</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4391,22 +4379,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123516643</v>
+        <v>123519050</v>
       </c>
       <c r="B34" t="n">
-        <v>105502</v>
+        <v>91608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4419,46 +4407,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446604</v>
+        <v>446696</v>
       </c>
       <c r="R34" t="n">
-        <v>6585606</v>
+        <v>6585518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4499,29 +4480,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123516553</v>
+        <v>123516577</v>
       </c>
       <c r="B35" t="n">
-        <v>83395</v>
+        <v>57643</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4530,34 +4510,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1445</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4565,10 +4550,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446597</v>
+        <v>446649</v>
       </c>
       <c r="R35" t="n">
-        <v>6585597</v>
+        <v>6585666</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4609,7 +4594,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4624,18 +4608,14 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123515263</v>
+        <v>123516564</v>
       </c>
       <c r="B36" t="n">
-        <v>5174</v>
+        <v>105518</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4648,34 +4628,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446669</v>
+        <v>446625</v>
       </c>
       <c r="R36" t="n">
-        <v>6585514</v>
+        <v>6585724</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4716,28 +4708,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123515258</v>
+        <v>123519051</v>
       </c>
       <c r="B37" t="n">
-        <v>105502</v>
+        <v>83400</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4746,38 +4739,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446629</v>
+        <v>446580</v>
       </c>
       <c r="R37" t="n">
-        <v>6585726</v>
+        <v>6585527</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4824,22 +4826,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123516522</v>
+        <v>123515263</v>
       </c>
       <c r="B38" t="n">
-        <v>83395</v>
+        <v>5176</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4848,49 +4850,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1445</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446600</v>
+        <v>446669</v>
       </c>
       <c r="R38" t="n">
-        <v>6585730</v>
+        <v>6585514</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4925,44 +4916,34 @@
           <t>2025-03-26</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Barkborredödade granar intill och kantzon från hygge.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123519051</v>
+        <v>123516643</v>
       </c>
       <c r="B39" t="n">
-        <v>83395</v>
+        <v>105518</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4971,47 +4952,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446580</v>
+        <v>446604</v>
       </c>
       <c r="R39" t="n">
-        <v>6585527</v>
+        <v>6585606</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5052,28 +5036,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123516564</v>
+        <v>123516626</v>
       </c>
       <c r="B40" t="n">
-        <v>105502</v>
+        <v>90421</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5086,35 +5071,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5125,7 +5109,7 @@
         <v>446625</v>
       </c>
       <c r="R40" t="n">
-        <v>6585724</v>
+        <v>6585622</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5185,10 +5169,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123519050</v>
+        <v>123516522</v>
       </c>
       <c r="B41" t="n">
-        <v>91603</v>
+        <v>83400</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5197,43 +5181,49 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446696</v>
+        <v>446600</v>
       </c>
       <c r="R41" t="n">
-        <v>6585518</v>
+        <v>6585730</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5268,27 +5258,37 @@
           <t>2025-03-26</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Barkborredödade granar intill och kantzon från hygge.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -3856,10 +3856,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123516553</v>
+        <v>123515263</v>
       </c>
       <c r="B29" t="n">
-        <v>83400</v>
+        <v>5176</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3868,45 +3868,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1445</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446597</v>
+        <v>446669</v>
       </c>
       <c r="R29" t="n">
-        <v>6585597</v>
+        <v>6585514</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3947,33 +3940,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123515258</v>
+        <v>123516577</v>
       </c>
       <c r="B30" t="n">
-        <v>105518</v>
+        <v>57644</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3982,38 +3970,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446629</v>
+        <v>446649</v>
       </c>
       <c r="R30" t="n">
-        <v>6585726</v>
+        <v>6585666</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,22 +4060,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123515262</v>
+        <v>123515258</v>
       </c>
       <c r="B31" t="n">
-        <v>83400</v>
+        <v>105520</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4084,25 +4084,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446659</v>
+        <v>446629</v>
       </c>
       <c r="R31" t="n">
-        <v>6585649</v>
+        <v>6585726</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4177,7 +4177,7 @@
         <v>123516584</v>
       </c>
       <c r="B32" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123519055</v>
+        <v>123516522</v>
       </c>
       <c r="B33" t="n">
-        <v>83400</v>
+        <v>83402</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4323,16 +4323,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
         <v>446600</v>
       </c>
       <c r="R33" t="n">
-        <v>6585508</v>
+        <v>6585730</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4367,34 +4369,44 @@
           <t>2025-03-26</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Barkborredödade granar intill och kantzon från hygge.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123519050</v>
+        <v>123516643</v>
       </c>
       <c r="B34" t="n">
-        <v>91608</v>
+        <v>105520</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4407,39 +4419,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446696</v>
+        <v>446604</v>
       </c>
       <c r="R34" t="n">
-        <v>6585518</v>
+        <v>6585606</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4480,28 +4499,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123516577</v>
+        <v>123516553</v>
       </c>
       <c r="B35" t="n">
-        <v>57643</v>
+        <v>83402</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4510,39 +4530,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>1445</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4550,10 +4565,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446649</v>
+        <v>446597</v>
       </c>
       <c r="R35" t="n">
-        <v>6585666</v>
+        <v>6585597</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4594,6 +4609,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4608,14 +4624,18 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123516564</v>
+        <v>123519050</v>
       </c>
       <c r="B36" t="n">
-        <v>105518</v>
+        <v>91610</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4628,46 +4648,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446625</v>
+        <v>446696</v>
       </c>
       <c r="R36" t="n">
-        <v>6585724</v>
+        <v>6585518</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4708,29 +4721,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123519051</v>
+        <v>123515262</v>
       </c>
       <c r="B37" t="n">
-        <v>83400</v>
+        <v>83402</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4760,26 +4772,17 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446580</v>
+        <v>446659</v>
       </c>
       <c r="R37" t="n">
-        <v>6585527</v>
+        <v>6585649</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4826,22 +4829,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123515263</v>
+        <v>123519055</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>83402</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4850,38 +4853,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>1445</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446669</v>
+        <v>446600</v>
       </c>
       <c r="R38" t="n">
-        <v>6585514</v>
+        <v>6585508</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4928,22 +4940,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123516643</v>
+        <v>123516564</v>
       </c>
       <c r="B39" t="n">
-        <v>105518</v>
+        <v>105520</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4975,7 +4987,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4992,10 +5004,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446604</v>
+        <v>446625</v>
       </c>
       <c r="R39" t="n">
-        <v>6585606</v>
+        <v>6585724</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5055,10 +5067,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123516626</v>
+        <v>123519051</v>
       </c>
       <c r="B40" t="n">
-        <v>90421</v>
+        <v>83402</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5067,30 +5079,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4189</v>
+        <v>1445</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5098,18 +5110,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446625</v>
+        <v>446580</v>
       </c>
       <c r="R40" t="n">
-        <v>6585622</v>
+        <v>6585527</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5150,29 +5160,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123516522</v>
+        <v>123516626</v>
       </c>
       <c r="B41" t="n">
-        <v>83400</v>
+        <v>90423</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5181,30 +5190,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1445</v>
+        <v>4189</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5220,10 +5229,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446600</v>
+        <v>446625</v>
       </c>
       <c r="R41" t="n">
-        <v>6585730</v>
+        <v>6585622</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5258,11 +5267,6 @@
           <t>2025-03-26</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Barkborredödade granar intill och kantzon från hygge.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5284,11 +5288,7 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -5067,10 +5067,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123519051</v>
+        <v>123516626</v>
       </c>
       <c r="B40" t="n">
-        <v>83402</v>
+        <v>90423</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5079,30 +5079,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1445</v>
+        <v>4189</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5110,16 +5110,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446580</v>
+        <v>446625</v>
       </c>
       <c r="R40" t="n">
-        <v>6585527</v>
+        <v>6585622</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5160,28 +5162,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123516626</v>
+        <v>123519051</v>
       </c>
       <c r="B41" t="n">
-        <v>90423</v>
+        <v>83402</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5190,30 +5193,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4189</v>
+        <v>1445</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5221,18 +5224,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446625</v>
+        <v>446580</v>
       </c>
       <c r="R41" t="n">
-        <v>6585622</v>
+        <v>6585527</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5273,19 +5274,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5290,6 +5290,113 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131761226</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106161</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>446659</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6585649</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -5295,7 +5295,7 @@
         <v>131761226</v>
       </c>
       <c r="B42" t="n">
-        <v>106161</v>
+        <v>106159</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -5295,7 +5295,7 @@
         <v>131761226</v>
       </c>
       <c r="B42" t="n">
-        <v>106159</v>
+        <v>106160</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -5295,7 +5295,7 @@
         <v>131761226</v>
       </c>
       <c r="B42" t="n">
-        <v>106160</v>
+        <v>106166</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -5295,7 +5295,7 @@
         <v>131761226</v>
       </c>
       <c r="B42" t="n">
-        <v>106166</v>
+        <v>106170</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -5295,7 +5295,7 @@
         <v>131761226</v>
       </c>
       <c r="B42" t="n">
-        <v>106170</v>
+        <v>106175</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -5295,7 +5295,7 @@
         <v>131761226</v>
       </c>
       <c r="B42" t="n">
-        <v>106175</v>
+        <v>106178</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -5295,7 +5295,7 @@
         <v>131761226</v>
       </c>
       <c r="B42" t="n">
-        <v>106219</v>
+        <v>106222</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>399944</v>
+        <v>113291517</v>
       </c>
       <c r="B2" t="n">
-        <v>81971</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1445</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446586.7191070581</v>
+        <v>446675</v>
       </c>
       <c r="R2" t="n">
-        <v>6585750.607498838</v>
+        <v>6585643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-04-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-04-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,83 +758,76 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>399943</v>
+        <v>113291547</v>
       </c>
       <c r="B3" t="n">
-        <v>81971</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1445</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446579.5795824223</v>
+        <v>446596</v>
       </c>
       <c r="R3" t="n">
-        <v>6585750.708432759</v>
+        <v>6585605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2008-04-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2008-04-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,83 +868,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>399945</v>
+        <v>108740410</v>
       </c>
       <c r="B4" t="n">
-        <v>81971</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1445</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446585.7711415172</v>
+        <v>446588</v>
       </c>
       <c r="R4" t="n">
-        <v>6585755.712687555</v>
+        <v>6585711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,22 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2008-04-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2008-04-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,83 +969,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>403257</v>
+        <v>123516584</v>
       </c>
       <c r="B5" t="n">
-        <v>81971</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1445</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klämmeshöjden, norra, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446581.7849822233</v>
+        <v>446651</v>
       </c>
       <c r="R5" t="n">
-        <v>6585762.388354733</v>
+        <v>6585639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,27 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-04-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-04-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>utflykt med Sällskapet för naturskydd, Kristinehamn</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,62 +1070,54 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>406106</v>
+        <v>123519050</v>
       </c>
       <c r="B6" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1227,14 +1125,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klämmeshöjden, norra, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446588.1122751065</v>
+        <v>446696</v>
       </c>
       <c r="R6" t="n">
-        <v>6585740.913389214</v>
+        <v>6585518</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,22 +1159,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-04-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-04-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,45 +1175,30 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>kalkbarrskog på hyperit med blåsippor</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>59430694</v>
+        <v>399943</v>
       </c>
       <c r="B7" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1348,7 +1221,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1356,17 +1229,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Klämmeshöjden, Vrm</t>
+          <t>Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446553.2599128875</v>
+        <v>446580</v>
       </c>
       <c r="R7" t="n">
-        <v>6585476.623121355</v>
+        <v>6585751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1393,22 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,42 +1279,38 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Dan Mangsbo</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Dan Mangsbo</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för bombmurkla</t>
-        </is>
-      </c>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>59430722</v>
+        <v>399944</v>
       </c>
       <c r="B8" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1475,7 +1333,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1483,17 +1341,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Klämmeshöjden, Vrm</t>
+          <t>Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446556.570720757</v>
+        <v>446587</v>
       </c>
       <c r="R8" t="n">
-        <v>6585458.244473725</v>
+        <v>6585751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1520,22 +1377,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,42 +1391,38 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Dan Mangsbo</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Dan Mangsbo</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för bombmurkla</t>
-        </is>
-      </c>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>59430714</v>
+        <v>399945</v>
       </c>
       <c r="B9" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1602,7 +1445,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1610,17 +1453,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Klämmeshöjden, Vrm</t>
+          <t>Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446552.0670830269</v>
+        <v>446586</v>
       </c>
       <c r="R9" t="n">
-        <v>6585464.418788041</v>
+        <v>6585756</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,22 +1489,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,76 +1503,81 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Dan Mangsbo</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Dan Mangsbo</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för bombmurkla</t>
-        </is>
-      </c>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>64923333</v>
+        <v>400675</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>1445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Klämmeshöjden söder om, Vrm</t>
+          <t>Klämmeshöjden, norra, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446589.8173732912</v>
+        <v>446580</v>
       </c>
       <c r="R10" t="n">
-        <v>6585572.856030488</v>
+        <v>6585785</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1764,27 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-04-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kristinehams Naturskyddsförening utflykt 9/4-17</t>
+          <t>2009-04-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1795,45 +1617,30 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Börje H Fagerlind</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>70478276</v>
+        <v>403257</v>
       </c>
       <c r="B11" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1856,22 +1663,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens NR, Vrm</t>
+          <t>Klämmeshöjden, norra, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446573.2883469584</v>
+        <v>446582</v>
       </c>
       <c r="R11" t="n">
-        <v>6585774.728729963</v>
+        <v>6585762</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1895,22 +1707,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-04-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-04-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>utflykt med Sällskapet för naturskydd, Kristinehamn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,31 +1732,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>70478278</v>
+        <v>406106</v>
       </c>
       <c r="B12" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1972,22 +1774,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens NR, Vrm</t>
+          <t>Klämmeshöjden, norra, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446607.8507201595</v>
+        <v>446588</v>
       </c>
       <c r="R12" t="n">
-        <v>6585766.093351127</v>
+        <v>6585741</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2011,22 +1818,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2037,35 +1834,40 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>kalkbarrskog på hyperit med blåsippor</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>70478282</v>
+        <v>406107</v>
       </c>
       <c r="B13" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2088,22 +1890,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens NR, Vrm</t>
+          <t>Klämmeshöjden, norra, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446567.0299955147</v>
+        <v>446570</v>
       </c>
       <c r="R13" t="n">
-        <v>6585476.428384191</v>
+        <v>6585791</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2127,22 +1934,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2153,35 +1950,40 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>kalkbarrskog på hyperit med blåsippor</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108487726</v>
+        <v>59430680</v>
       </c>
       <c r="B14" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2202,20 +2004,27 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446544.5669185328</v>
+        <v>446536</v>
       </c>
       <c r="R14" t="n">
-        <v>6585439.063908149</v>
+        <v>6585516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2242,31 +2051,16 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hyggeskant</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
@@ -2278,35 +2072,30 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Dan Mangsbo</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Dan Mangsbo</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Uppföljning bombmurkla 2023</t>
+          <t>Åtgärdsprogram för bombmurkla</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>70478280</v>
+        <v>59430694</v>
       </c>
       <c r="B15" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2329,22 +2118,28 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens NR, Vrm</t>
+          <t>Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446560.437147126</v>
+        <v>446553</v>
       </c>
       <c r="R15" t="n">
-        <v>6585515.221834606</v>
+        <v>6585477</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2368,22 +2163,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,37 +2177,37 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Dan Mangsbo</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Dan Mangsbo</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för bombmurkla</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>70478281</v>
+        <v>59430714</v>
       </c>
       <c r="B16" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2445,22 +2230,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens NR, Vrm</t>
+          <t>Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446550.6175664561</v>
+        <v>446552</v>
       </c>
       <c r="R16" t="n">
-        <v>6585506.194911079</v>
+        <v>6585464</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2484,22 +2275,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,37 +2289,37 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Dan Mangsbo</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Dan Mangsbo</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för bombmurkla</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>70478279</v>
+        <v>59430722</v>
       </c>
       <c r="B17" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2561,22 +2342,28 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens NR, Vrm</t>
+          <t>Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446603.8460928074</v>
+        <v>446557</v>
       </c>
       <c r="R17" t="n">
-        <v>6585590.989026062</v>
+        <v>6585458</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2600,22 +2387,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2624,75 +2401,75 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Dan Mangsbo</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Dan Mangsbo</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för bombmurkla</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113291517</v>
+        <v>70478275</v>
       </c>
       <c r="B18" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>1445</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>Klämmeshöjdens NR, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446675</v>
+        <v>446562</v>
       </c>
       <c r="R18" t="n">
-        <v>6585643</v>
+        <v>6585789</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2716,12 +2493,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2730,76 +2507,70 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113291537</v>
+        <v>70478276</v>
       </c>
       <c r="B19" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens NR, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446618</v>
+        <v>446573</v>
       </c>
       <c r="R19" t="n">
-        <v>6585536</v>
+        <v>6585775</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2823,12 +2594,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,76 +2608,70 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113291551</v>
+        <v>70478278</v>
       </c>
       <c r="B20" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens NR, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446630</v>
+        <v>446608</v>
       </c>
       <c r="R20" t="n">
-        <v>6585625</v>
+        <v>6585766</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2930,12 +2695,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2944,81 +2709,70 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113291530</v>
+        <v>70478279</v>
       </c>
       <c r="B21" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>1445</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens NR, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446657</v>
+        <v>446604</v>
       </c>
       <c r="R21" t="n">
-        <v>6585635</v>
+        <v>6585591</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3042,12 +2796,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,84 +2810,70 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113291547</v>
+        <v>70478280</v>
       </c>
       <c r="B22" t="n">
-        <v>94275</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>210</v>
+        <v>1445</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>38</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens NR, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446596</v>
+        <v>446560</v>
       </c>
       <c r="R22" t="n">
-        <v>6585605</v>
+        <v>6585515</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3157,12 +2897,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,38 +2911,32 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>116046258</v>
+        <v>70478281</v>
       </c>
       <c r="B23" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3225,12 +2959,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3239,13 +2968,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446597</v>
+        <v>446551</v>
       </c>
       <c r="R23" t="n">
-        <v>6585609</v>
+        <v>6585506</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3269,12 +2998,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,31 +3018,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116046264</v>
+        <v>70478282</v>
       </c>
       <c r="B24" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3336,12 +3060,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3350,13 +3069,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446656</v>
+        <v>446567</v>
       </c>
       <c r="R24" t="n">
-        <v>6585649</v>
+        <v>6585476</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3380,12 +3099,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3400,59 +3119,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116046263</v>
+        <v>70478283</v>
       </c>
       <c r="B25" t="n">
-        <v>104746</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3461,13 +3170,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446613</v>
+        <v>446545</v>
       </c>
       <c r="R25" t="n">
-        <v>6585538</v>
+        <v>6585439</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3491,12 +3200,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3511,31 +3220,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Herbert Kaufmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116046262</v>
+        <v>116046258</v>
       </c>
       <c r="B26" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3558,7 +3262,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3572,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446607</v>
+        <v>446597</v>
       </c>
       <c r="R26" t="n">
-        <v>6585756</v>
+        <v>6585609</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3634,19 +3338,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116046269</v>
+        <v>116046259</v>
       </c>
       <c r="B27" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3669,7 +3368,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3683,10 +3382,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446553</v>
+        <v>446574</v>
       </c>
       <c r="R27" t="n">
-        <v>6585515</v>
+        <v>6585524</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3745,19 +3444,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116046259</v>
+        <v>116046262</v>
       </c>
       <c r="B28" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3780,7 +3474,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3794,10 +3488,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446574</v>
+        <v>446607</v>
       </c>
       <c r="R28" t="n">
-        <v>6585524</v>
+        <v>6585756</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3856,19 +3550,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123516553</v>
+        <v>116046264</v>
       </c>
       <c r="B29" t="n">
-        <v>83424</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3894,19 +3583,21 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens NR, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446597</v>
+        <v>446656</v>
       </c>
       <c r="R29" t="n">
-        <v>6585597</v>
+        <v>6585649</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3933,12 +3624,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3947,85 +3638,72 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123516564</v>
+        <v>116046269</v>
       </c>
       <c r="B30" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens NR, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446625</v>
+        <v>446553</v>
       </c>
       <c r="R30" t="n">
-        <v>6585724</v>
+        <v>6585515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4052,12 +3730,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4066,72 +3744,63 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123516584</v>
+        <v>123515262</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1445</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446651</v>
+        <v>446659</v>
       </c>
       <c r="R31" t="n">
-        <v>6585639</v>
+        <v>6585649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,69 +3841,74 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123515263</v>
+        <v>123516522</v>
       </c>
       <c r="B32" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>1445</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446669</v>
+        <v>446600</v>
       </c>
       <c r="R32" t="n">
-        <v>6585514</v>
+        <v>6585730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4269,75 +3943,79 @@
           <t>2025-03-26</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Barkborredödade granar intill och kantzon från hygge.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123516577</v>
+        <v>123516543</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>1445</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4345,10 +4023,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446649</v>
+        <v>446597</v>
       </c>
       <c r="R33" t="n">
-        <v>6585666</v>
+        <v>6585597</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4389,6 +4067,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4403,46 +4082,45 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123516626</v>
+        <v>123519051</v>
       </c>
       <c r="B34" t="n">
-        <v>90445</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4189</v>
+        <v>1445</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4450,18 +4128,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446625</v>
+        <v>446580</v>
       </c>
       <c r="R34" t="n">
-        <v>6585622</v>
+        <v>6585527</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4502,38 +4178,32 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123515262</v>
+        <v>123519055</v>
       </c>
       <c r="B35" t="n">
-        <v>83424</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4554,17 +4224,26 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>N om Skinnerud, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446659</v>
+        <v>446600</v>
       </c>
       <c r="R35" t="n">
-        <v>6585649</v>
+        <v>6585508</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4611,27 +4290,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123519050</v>
+        <v>123516626</v>
       </c>
       <c r="B36" t="n">
-        <v>91632</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4639,39 +4313,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1339</v>
+        <v>4189</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446696</v>
+        <v>446625</v>
       </c>
       <c r="R36" t="n">
-        <v>6585518</v>
+        <v>6585622</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4712,77 +4392,67 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123519055</v>
+        <v>108740432</v>
       </c>
       <c r="B37" t="n">
-        <v>83424</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1445</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446600</v>
+        <v>446500</v>
       </c>
       <c r="R37" t="n">
-        <v>6585508</v>
+        <v>6585450</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4809,12 +4479,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>fina exemplar på rönn</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4823,33 +4498,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123516643</v>
+        <v>123515263</v>
       </c>
       <c r="B38" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,46 +4528,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Söder Klämmeshöjden, Vrm</t>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446604</v>
+        <v>446669</v>
       </c>
       <c r="R38" t="n">
-        <v>6585606</v>
+        <v>6585514</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4937,34 +4596,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123515258</v>
+        <v>123770132</v>
       </c>
       <c r="B39" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,34 +4625,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>Söder Klämmeshöjden, Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446629</v>
+        <v>446706</v>
       </c>
       <c r="R39" t="n">
-        <v>6585726</v>
+        <v>6585647</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5026,12 +4688,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5046,71 +4708,69 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123519051</v>
+        <v>123516577</v>
       </c>
       <c r="B40" t="n">
-        <v>83424</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1445</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N om Skinnerud, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446580</v>
+        <v>446649</v>
       </c>
       <c r="R40" t="n">
-        <v>6585527</v>
+        <v>6585666</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5157,62 +4817,55 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123516522</v>
+        <v>113291530</v>
       </c>
       <c r="B41" t="n">
-        <v>83424</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1445</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5220,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446600</v>
+        <v>446657</v>
       </c>
       <c r="R41" t="n">
-        <v>6585730</v>
+        <v>6585635</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5250,17 +4903,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Barkborredödade granar intill och kantzon från hygge.</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5284,18 +4932,14 @@
           <t>Fredrik Wilde</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131761226</v>
+        <v>113291537</v>
       </c>
       <c r="B42" t="n">
-        <v>106222</v>
+        <v>106244</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5321,16 +4965,20 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+          <t>Söder Klämmeshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446659</v>
+        <v>446618</v>
       </c>
       <c r="R42" t="n">
-        <v>6585649</v>
+        <v>6585536</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5357,22 +5005,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5381,21 +5019,876 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>113291551</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>446630</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6585625</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>116046263</v>
+      </c>
+      <c r="B44" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>S om Klämmeshöjdens NR, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>446613</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6585538</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
           <t>anders tedeholm</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>anders tedeholm</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123515258</v>
+      </c>
+      <c r="B45" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>446629</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6585726</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123516564</v>
+      </c>
+      <c r="B46" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>446625</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6585724</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123516571</v>
+      </c>
+      <c r="B47" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>446579</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6585730</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123516643</v>
+      </c>
+      <c r="B48" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Söder Klämmeshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>446604</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6585606</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131761226</v>
+      </c>
+      <c r="B49" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>S om Klämmeshöjdens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>446659</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6585649</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>64923333</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Klämmeshöjden söder om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>446590</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6585573</v>
+      </c>
+      <c r="S50" t="n">
+        <v>50</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2017-04-09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Kristinehams Naturskyddsförening utflykt 9/4-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53132-2023 artfynd.xlsx
+++ b/artfynd/A 53132-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113291517</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113291547</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108740410</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123516584</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123519050</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/399943</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/399944</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/399945</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/400675</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/403257</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1857,6 +1912,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406106</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,6 +2033,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406107</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2085,6 +2150,11 @@
           <t>Åtgärdsprogram för bombmurkla</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59430680</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2197,6 +2267,11 @@
           <t>Åtgärdsprogram för bombmurkla</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59430694</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2309,6 +2384,11 @@
           <t>Åtgärdsprogram för bombmurkla</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59430714</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2421,6 +2501,11 @@
           <t>Åtgärdsprogram för bombmurkla</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59430722</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2522,6 +2607,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70478275</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2623,6 +2713,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70478276</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2724,6 +2819,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70478278</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2825,6 +2925,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70478279</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2926,6 +3031,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70478280</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3027,6 +3137,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70478281</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3128,6 +3243,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70478282</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3229,6 +3349,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70478283</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3335,6 +3460,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116046258</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3441,6 +3571,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116046259</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3547,6 +3682,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116046262</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3653,6 +3793,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116046264</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3759,6 +3904,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116046269</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3856,6 +4006,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123515262</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3974,6 +4129,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123516522</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4087,6 +4247,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123516543</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4193,6 +4358,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123519051</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4299,6 +4469,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123519055</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4408,6 +4583,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123516626</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4514,6 +4694,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108740432</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4611,6 +4796,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123515263</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4717,6 +4907,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123770132</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4826,6 +5021,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123516577</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4933,6 +5133,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113291530</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5035,6 +5240,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113291537</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5137,6 +5347,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113291551</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5243,6 +5458,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116046263</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5340,6 +5560,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123515258</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5450,6 +5675,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123516564</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5560,6 +5790,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123516571</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5670,6 +5905,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123516643</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5777,6 +6017,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131761226</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5889,8 +6134,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64923333</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>